--- a/data/trans_dic/IP13-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP13-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,97%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,7</t>
+          <t>2,64; 10,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,44</t>
+          <t>1,42; 9,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 11,03</t>
+          <t>0,64; 6,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 11,58</t>
+          <t>1,44; 8,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 10,48</t>
+          <t>0,51; 4,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,57</t>
+          <t>1,6; 9,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,78</t>
+          <t>2,5; 11,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,82</t>
+          <t>3,64; 12,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,89</t>
+          <t>2,04; 6,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,39</t>
+          <t>2,16; 7,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,72</t>
+          <t>2,02; 7,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,63</t>
+          <t>3,0; 8,33</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,44%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 9,62</t>
+          <t>2,39; 10,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 13,75</t>
+          <t>0,73; 7,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,79</t>
+          <t>2,24; 8,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 10,62</t>
+          <t>5,35; 16,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 10,47</t>
+          <t>1,49; 8,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,96</t>
+          <t>4,73; 14,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 8,94</t>
+          <t>0,54; 5,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 15,32</t>
+          <t>2,1; 9,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 8,03</t>
+          <t>2,74; 7,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,35</t>
+          <t>3,38; 8,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,53</t>
+          <t>1,73; 5,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,97</t>
+          <t>4,79; 11,79</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,93%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,49%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,16%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 11,66</t>
+          <t>1,33; 7,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 11,94</t>
+          <t>1,59; 9,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 13,07</t>
+          <t>2,68; 12,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 11,65</t>
+          <t>2,11; 14,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,49</t>
+          <t>2,01; 11,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 9,23</t>
+          <t>3,18; 12,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 13,54</t>
+          <t>2,48; 12,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 11,69</t>
+          <t>1,77; 11,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,74</t>
+          <t>2,37; 7,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 9,32</t>
+          <t>3,34; 9,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,6</t>
+          <t>3,47; 10,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,87</t>
+          <t>2,68; 9,92</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,33%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,4%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,77%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,21</t>
+          <t>3,3; 8,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,32</t>
+          <t>5,75; 12,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,08</t>
+          <t>2,34; 7,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,14</t>
+          <t>4,44; 10,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,62</t>
+          <t>3,06; 8,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 11,85</t>
+          <t>2,49; 7,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,56</t>
+          <t>5,28; 10,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 11,13</t>
+          <t>2,62; 7,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,39</t>
+          <t>3,84; 7,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,06</t>
+          <t>4,66; 8,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,33</t>
+          <t>4,43; 8,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,9</t>
+          <t>4,14; 8,31</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,48%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,12%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,64%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,9</t>
+          <t>2,3; 8,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 11,33</t>
+          <t>2,6; 9,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,74</t>
+          <t>1,9; 8,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,63</t>
+          <t>3,66; 10,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,48</t>
+          <t>1,28; 7,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 9,17</t>
+          <t>4,45; 11,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,81</t>
+          <t>1,54; 6,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,85</t>
+          <t>4,77; 12,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,8</t>
+          <t>2,45; 6,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,48</t>
+          <t>4,01; 8,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,24</t>
+          <t>2,28; 6,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 10,37</t>
+          <t>4,91; 10,17</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4,31%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 9,69</t>
+          <t>3,49; 13,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,28</t>
+          <t>3,66; 14,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,87</t>
+          <t>0,9; 9,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 11,37</t>
+          <t>1,33; 12,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 12,71</t>
+          <t>1,69; 8,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 14,34</t>
+          <t>0,0; 7,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,61</t>
+          <t>1,08; 10,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,38</t>
+          <t>2,06; 12,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,28</t>
+          <t>3,11; 9,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,94</t>
+          <t>2,41; 9,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,39</t>
+          <t>1,3; 7,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 9,03</t>
+          <t>2,64; 9,48</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4,28%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,61%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,71</t>
+          <t>3,83; 6,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,19</t>
+          <t>4,47; 7,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 6,85</t>
+          <t>3,09; 5,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,25</t>
+          <t>4,76; 8,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,78</t>
+          <t>3,14; 5,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,51</t>
+          <t>4,19; 7,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,66</t>
+          <t>3,96; 6,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,88</t>
+          <t>4,6; 7,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,76</t>
+          <t>3,86; 5,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,07</t>
+          <t>4,77; 6,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 5,79</t>
+          <t>3,8; 5,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,13</t>
+          <t>5,22; 7,39</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3575</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1945</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4249</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4960</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6639</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3575</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2173</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>11779</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>510; 4907</t>
+          <t>2577; 9803</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1455; 8493</t>
+          <t>1276; 8434</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1853; 9163</t>
+          <t>634; 6369</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3252; 12100</t>
+          <t>1762; 9973</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2578; 10224</t>
+          <t>528; 4938</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1280; 7691</t>
+          <t>1440; 8659</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>634; 5772</t>
+          <t>2074; 9654</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1784; 10643</t>
+          <t>3746; 12457</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3689; 11901</t>
+          <t>4118; 12883</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4019; 13271</t>
+          <t>3881; 13346</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3759; 12286</t>
+          <t>3701; 13141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6537; 18372</t>
+          <t>6755; 18737</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2916</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5189</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8785</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3880</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7708</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1859</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5015</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4526</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2916</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5189</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>13687</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1358; 8408</t>
+          <t>2054; 8751</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3841; 12821</t>
+          <t>702; 6987</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>567; 5064</t>
+          <t>2521; 9554</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2065; 10053</t>
+          <t>4886; 14804</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1905; 9003</t>
+          <t>1305; 7860</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>718; 6690</t>
+          <t>4411; 13298</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2418; 10084</t>
+          <t>571; 5301</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5044; 14646</t>
+          <t>2029; 9481</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4811; 13923</t>
+          <t>4744; 13415</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6030; 17705</t>
+          <t>6408; 16939</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3732; 12073</t>
+          <t>3790; 11912</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8329; 20863</t>
+          <t>8994; 22150</t>
         </is>
       </c>
     </row>
@@ -2207,37 +2207,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3382</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3961</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3451</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3994</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5589</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3812</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2747</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3382</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3961</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5031</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6035</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1466; 7856</t>
+          <t>1325; 7490</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2359; 10287</t>
+          <t>1381; 8157</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1804; 8084</t>
+          <t>2020; 9716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1077; 6039</t>
+          <t>1203; 8008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1337; 7438</t>
+          <t>1355; 8025</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1820; 8017</t>
+          <t>2737; 11178</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2409; 10216</t>
+          <t>1536; 7807</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1170; 7461</t>
+          <t>949; 6142</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4155; 12905</t>
+          <t>3956; 13213</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5443; 16120</t>
+          <t>5778; 16285</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4696; 14549</t>
+          <t>4757; 14287</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3176; 11425</t>
+          <t>2964; 10958</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11039</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19457</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9625</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14029</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>10700</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9076</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>17378</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8901</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11039</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19457</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9625</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15897</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24798</t>
+          <t>22916</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6408; 16479</t>
+          <t>6674; 16839</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5041; 15091</t>
+          <t>13060; 28011</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11773; 24766</t>
+          <t>4926; 15623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4436; 15566</t>
+          <t>8973; 21596</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6814; 17428</t>
+          <t>6138; 17101</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13494; 26912</t>
+          <t>5126; 15634</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5744; 15947</t>
+          <t>11801; 23928</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9639; 24297</t>
+          <t>4681; 13735</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15851; 29757</t>
+          <t>15463; 30061</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21210; 39235</t>
+          <t>20175; 38554</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19847; 36178</t>
+          <t>19225; 34872</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16575; 34471</t>
+          <t>15777; 31626</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6069</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6878</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6061</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9364</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3624</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>10573</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>4956</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>10391</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6069</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6878</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6061</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20305</t>
+          <t>19159</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1366; 8230</t>
+          <t>2925; 11005</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5976; 16833</t>
+          <t>3632; 12985</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1779; 9184</t>
+          <t>2716; 11487</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6246; 16278</t>
+          <t>5423; 15688</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3059; 10800</t>
+          <t>1336; 7989</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3422; 12806</t>
+          <t>6614; 16588</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2921; 11168</t>
+          <t>2096; 9189</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5594; 16016</t>
+          <t>5665; 15245</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5748; 15735</t>
+          <t>5661; 15817</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11482; 24437</t>
+          <t>11566; 25051</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6667; 17425</t>
+          <t>6360; 17057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14233; 29259</t>
+          <t>13108; 27143</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5175</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5664</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2132</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3225</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2335</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3744</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5175</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5664</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7284</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1283; 7253</t>
+          <t>2529; 9844</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3349</t>
+          <t>2710; 10868</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>659; 6029</t>
+          <t>614; 6356</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1327; 7831</t>
+          <t>909; 8289</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2497; 9205</t>
+          <t>1269; 6564</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2617; 10619</t>
+          <t>0; 4098</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>605; 5839</t>
+          <t>661; 6615</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>882; 8191</t>
+          <t>1452; 8451</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4532; 13671</t>
+          <t>4573; 13412</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2797; 11381</t>
+          <t>3073; 11583</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1654; 9528</t>
+          <t>1674; 9275</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3608; 12722</t>
+          <t>3656; 13148</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>58</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>35450</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>42452</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>30211</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>44083</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>27368</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>38013</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>35299</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>37437</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>35450</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>42452</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>46608</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>84045</t>
+          <t>80860</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20387; 36463</t>
+          <t>26230; 45857</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28351; 48696</t>
+          <t>31930; 53715</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27432; 46007</t>
+          <t>21925; 40457</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28165; 47684</t>
+          <t>32757; 56412</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>27696; 46450</t>
+          <t>20085; 37092</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33153; 53612</t>
+          <t>28388; 48247</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21636; 40172</t>
+          <t>26570; 45224</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>35439; 58986</t>
+          <t>28572; 47432</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52012; 76230</t>
+          <t>51080; 75009</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>67840; 98282</t>
+          <t>66306; 94719</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53353; 79936</t>
+          <t>52547; 78253</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>68514; 100169</t>
+          <t>68415; 96737</t>
         </is>
       </c>
     </row>
